--- a/vacmap_schwangere_INF_PER.xlsx
+++ b/vacmap_schwangere_INF_PER.xlsx
@@ -357,7 +357,7 @@
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Berichtszeitraum</t>
+          <t>Berichtszeitpunkt</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
